--- a/branches/migration/2026.0.3-template-v0.11.3/StructureDefinition-mii-pr-icu-bilanz-einfuhr-fluessigkeit-gesamt.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.3/StructureDefinition-mii-pr-icu-bilanz-einfuhr-fluessigkeit-gesamt.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-31T19:21:50+00:00</t>
+    <t>2026-09-14T06:39:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.3/StructureDefinition-mii-pr-icu-bilanz-einfuhr-fluessigkeit-gesamt.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.3/StructureDefinition-mii-pr-icu-bilanz-einfuhr-fluessigkeit-gesamt.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-14T06:39:50+00:00</t>
+    <t>2026-09-14T07:03:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.3/StructureDefinition-mii-pr-icu-bilanz-einfuhr-fluessigkeit-gesamt.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.3/StructureDefinition-mii-pr-icu-bilanz-einfuhr-fluessigkeit-gesamt.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-14T07:03:32+00:00</t>
+    <t>2026-09-14T10:16:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.3/StructureDefinition-mii-pr-icu-bilanz-einfuhr-fluessigkeit-gesamt.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.3/StructureDefinition-mii-pr-icu-bilanz-einfuhr-fluessigkeit-gesamt.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-14T10:16:02+00:00</t>
+    <t>2026-09-14T15:22:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.3/StructureDefinition-mii-pr-icu-bilanz-einfuhr-fluessigkeit-gesamt.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.3/StructureDefinition-mii-pr-icu-bilanz-einfuhr-fluessigkeit-gesamt.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-14T15:22:31+00:00</t>
+    <t>2026-09-14T19:16:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.3/StructureDefinition-mii-pr-icu-bilanz-einfuhr-fluessigkeit-gesamt.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.3/StructureDefinition-mii-pr-icu-bilanz-einfuhr-fluessigkeit-gesamt.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-14T19:16:28+00:00</t>
+    <t>2026-09-14T19:40:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.3/StructureDefinition-mii-pr-icu-bilanz-einfuhr-fluessigkeit-gesamt.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.3/StructureDefinition-mii-pr-icu-bilanz-einfuhr-fluessigkeit-gesamt.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-14T19:40:21+00:00</t>
+    <t>2026-09-14T20:52:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
